--- a/template/Summary_Template.xlsx
+++ b/template/Summary_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.0.0.25\02-General Merchandise\04-GM_PO Committee\New folder\R&amp;F\GM VISIBILITY REPORTS\2026\10.OCTOBER_2026\09-Oct (Till 08-Oct)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.0.0.25\02-General Merchandise\04-GM_PO Committee\New folder\R&amp;F\GM VISIBILITY REPORTS\2026\10.OCTOBER_2026\13-Oct (Till 12-Oct)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3FD263-5F9E-44F3-A153-6F7FA961DCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096C4F46-72DD-4EFC-AE72-4DCC41F3910F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REGULAR" sheetId="1" r:id="rId1"/>
@@ -133,28 +133,7 @@
     <t>LS_MA_BELT</t>
   </si>
   <si>
-    <t>LS_IA_BABY BEDING</t>
-  </si>
-  <si>
     <t>FW_M_SHOES</t>
-  </si>
-  <si>
-    <t>NF_B_FACEWASH</t>
-  </si>
-  <si>
-    <t>NF_B_HANDWASH</t>
-  </si>
-  <si>
-    <t>NF_C_TOILET CLEANER</t>
-  </si>
-  <si>
-    <t>ST_NP_KIT</t>
-  </si>
-  <si>
-    <t>HH_KA_STRAINER</t>
-  </si>
-  <si>
-    <t>HH_U_T_CASSEROLE</t>
   </si>
   <si>
     <t>OCT
@@ -195,22 +174,43 @@
     <t>OND VISIBILITY %</t>
   </si>
   <si>
-    <t>Till 08-OCT</t>
-  </si>
-  <si>
     <t>FW_B_SHOES</t>
   </si>
   <si>
+    <t>Till 12-OCT</t>
+  </si>
+  <si>
+    <t>FW_G_SHOES</t>
+  </si>
+  <si>
+    <t>HF_BF_DOUB BEDSHEET</t>
+  </si>
+  <si>
+    <t>NF_B_FACEWASH</t>
+  </si>
+  <si>
+    <t>NF_B_HANDWASH</t>
+  </si>
+  <si>
+    <t>NF_C_TOILET CLEANER</t>
+  </si>
+  <si>
+    <t>NF_F_PERFUME</t>
+  </si>
+  <si>
     <t>TG_NS_P_SET</t>
   </si>
   <si>
-    <t>HH_P_LUNCH BOX</t>
+    <t>HH_C_BC_COFFEE SET</t>
+  </si>
+  <si>
+    <t>HH_P_PATLA</t>
+  </si>
+  <si>
+    <t>HH_U_T_CASSEROLE</t>
   </si>
   <si>
     <t>HH_U_T_FLASK</t>
-  </si>
-  <si>
-    <t>HH_C_BC_COFFEE SET</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1574,7 @@
     <row r="8" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C8" s="56"/>
       <c r="E8" s="76" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F8" s="77"/>
       <c r="G8" s="77"/>
@@ -1582,7 +1582,7 @@
       <c r="I8" s="77"/>
       <c r="J8" s="78"/>
       <c r="K8" s="76" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L8" s="77"/>
       <c r="M8" s="77"/>
@@ -1625,16 +1625,16 @@
         <v>12</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I10" s="28" t="s">
         <v>18</v>
@@ -1643,16 +1643,16 @@
         <v>14</v>
       </c>
       <c r="K10" s="28" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L10" s="28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O10" s="28" t="s">
         <v>18</v>
@@ -1668,40 +1668,40 @@
         <v>0</v>
       </c>
       <c r="E11" s="30">
-        <v>0.20154452399092884</v>
+        <v>0.24480984124651339</v>
       </c>
       <c r="F11" s="31">
-        <v>0.12221536270989296</v>
+        <v>0.16039611663811171</v>
       </c>
       <c r="G11" s="30">
-        <v>0.25708005213414753</v>
+        <v>0.27937120665148024</v>
       </c>
       <c r="H11" s="31">
-        <v>0.17157948652664981</v>
+        <v>0.19415162152467696</v>
       </c>
       <c r="I11" s="30">
-        <v>0.76294396924031405</v>
+        <v>0.76287398877224444</v>
       </c>
       <c r="J11" s="32">
-        <v>16179.985869836644</v>
+        <v>18451.985869836644</v>
       </c>
       <c r="K11" s="30">
-        <v>0.1831046035478171</v>
+        <v>0.22186935075155043</v>
       </c>
       <c r="L11" s="31">
-        <v>0.11751487893525497</v>
+        <v>0.15481012193373206</v>
       </c>
       <c r="M11" s="30">
-        <v>0.23765493227670018</v>
+        <v>0.25823827210678585</v>
       </c>
       <c r="N11" s="31">
-        <v>0.16245918371603235</v>
+        <v>0.18414580778431786</v>
       </c>
       <c r="O11" s="30">
-        <v>0.67623691468774949</v>
+        <v>0.67619394422489965</v>
       </c>
       <c r="P11" s="32">
-        <v>16179.985869836644</v>
+        <v>18451.985869836644</v>
       </c>
       <c r="Q11" s="29"/>
     </row>
@@ -1711,40 +1711,40 @@
         <v>27</v>
       </c>
       <c r="E12" s="33">
-        <v>0.29557684891275326</v>
+        <v>0.31615295618380845</v>
       </c>
       <c r="F12" s="34">
-        <v>0.17171215149304583</v>
+        <v>0.19693961935362087</v>
       </c>
       <c r="G12" s="33">
-        <v>0.39209706606544248</v>
+        <v>0.45617490877807115</v>
       </c>
       <c r="H12" s="34">
-        <v>0.24037674453728516</v>
+        <v>0.27702681891100189</v>
       </c>
       <c r="I12" s="33">
         <v>0.95078397034395934</v>
       </c>
       <c r="J12" s="35">
-        <v>-55216.198263512342</v>
+        <v>-55206.198263512342</v>
       </c>
       <c r="K12" s="33">
-        <v>0.19616126257082678</v>
+        <v>0.21158740989053368</v>
       </c>
       <c r="L12" s="34">
-        <v>0.14946127532874839</v>
+        <v>0.1746887431893234</v>
       </c>
       <c r="M12" s="33">
-        <v>0.28753151977216768</v>
+        <v>0.35160936248479635</v>
       </c>
       <c r="N12" s="34">
-        <v>0.21812586837298767</v>
+        <v>0.25477594274670445</v>
       </c>
       <c r="O12" s="33">
         <v>0.84721368435551681</v>
       </c>
       <c r="P12" s="35">
-        <v>-55216.198263512342</v>
+        <v>-55206.198263512342</v>
       </c>
       <c r="Q12" s="29"/>
     </row>
@@ -1754,40 +1754,40 @@
         <v>11</v>
       </c>
       <c r="E13" s="36">
-        <v>0.23500877467002923</v>
+        <v>0.39690588118766618</v>
       </c>
       <c r="F13" s="37">
-        <v>0.12759393332580335</v>
+        <v>0.22643465179893832</v>
       </c>
       <c r="G13" s="38">
-        <v>0.41940129067650039</v>
+        <v>0.59569850690925896</v>
       </c>
       <c r="H13" s="39">
-        <v>0.23642416326358479</v>
+        <v>0.3347777789394879</v>
       </c>
       <c r="I13" s="38">
-        <v>0.91982178345895216</v>
+        <v>0.91998537162488203</v>
       </c>
       <c r="J13" s="40">
-        <v>-907685.74447416631</v>
+        <v>-908342.74447416631</v>
       </c>
       <c r="K13" s="36">
-        <v>0.19367639626460645</v>
+        <v>0.34941853525233207</v>
       </c>
       <c r="L13" s="37">
-        <v>0.10817098030227595</v>
+        <v>0.20114453131010943</v>
       </c>
       <c r="M13" s="38">
-        <v>0.36208402857672567</v>
+        <v>0.5081257761963901</v>
       </c>
       <c r="N13" s="39">
-        <v>0.20840342460674319</v>
+        <v>0.29855017662317429</v>
       </c>
       <c r="O13" s="38">
-        <v>0.80004344938846084</v>
+        <v>0.80043353769817693</v>
       </c>
       <c r="P13" s="40">
-        <v>-907685.744474167</v>
+        <v>-908342.744474167</v>
       </c>
       <c r="Q13" s="29"/>
     </row>
@@ -1797,40 +1797,40 @@
         <v>1</v>
       </c>
       <c r="E14" s="41">
-        <v>0.29891680868116954</v>
+        <v>0.39598791933304134</v>
       </c>
       <c r="F14" s="42">
-        <v>0.15463729808695156</v>
+        <v>0.20557113844907493</v>
       </c>
       <c r="G14" s="41">
-        <v>0.49258105352885184</v>
+        <v>0.59295181288414001</v>
       </c>
       <c r="H14" s="42">
-        <v>0.25828113019585963</v>
+        <v>0.31135877216931823</v>
       </c>
       <c r="I14" s="41">
-        <v>0.91359695125093066</v>
+        <v>0.91381578676474506</v>
       </c>
       <c r="J14" s="43">
-        <v>-554962.21828119573</v>
+        <v>-552928.21828119573</v>
       </c>
       <c r="K14" s="41">
-        <v>0.26924360064712644</v>
+        <v>0.34872195540275586</v>
       </c>
       <c r="L14" s="42">
-        <v>0.14436306670456331</v>
+        <v>0.19506267050664539</v>
       </c>
       <c r="M14" s="41">
-        <v>0.4209318457130668</v>
+        <v>0.50854117074371641</v>
       </c>
       <c r="N14" s="42">
-        <v>0.23939568236754402</v>
+        <v>0.28760659091203433</v>
       </c>
       <c r="O14" s="41">
-        <v>0.81386093126731651</v>
+        <v>0.81371058113332673</v>
       </c>
       <c r="P14" s="43">
-        <v>-554962.21828119573</v>
+        <v>-552928.21828119573</v>
       </c>
       <c r="Q14" s="29"/>
     </row>
@@ -1840,40 +1840,40 @@
         <v>2</v>
       </c>
       <c r="E15" s="44">
-        <v>0.25740583167526399</v>
+        <v>0.35940647641655027</v>
       </c>
       <c r="F15" s="44">
-        <v>0.14073469357812013</v>
+        <v>0.20397081279794724</v>
       </c>
       <c r="G15" s="44">
-        <v>0.41258354695416499</v>
+        <v>0.51939431320021368</v>
       </c>
       <c r="H15" s="44">
-        <v>0.23410330676755803</v>
+        <v>0.29600120121001711</v>
       </c>
       <c r="I15" s="44">
-        <v>0.89103917736327809</v>
+        <v>0.89117307970904136</v>
       </c>
       <c r="J15" s="45">
-        <v>-1501684.1751490394</v>
+        <v>-1498025.1751490394</v>
       </c>
       <c r="K15" s="44">
-        <v>0.22125003200791082</v>
+        <v>0.31303127087740951</v>
       </c>
       <c r="L15" s="44">
-        <v>0.1275769076232614</v>
+        <v>0.1885641143800206</v>
       </c>
       <c r="M15" s="44">
-        <v>0.3541346841589707</v>
+        <v>0.44557913043010267</v>
       </c>
       <c r="N15" s="44">
-        <v>0.21365279662169914</v>
+        <v>0.27058226538417318</v>
       </c>
       <c r="O15" s="44">
-        <v>0.78659075457362893</v>
+        <v>0.78665301433907575</v>
       </c>
       <c r="P15" s="45">
-        <v>-1501684.1751490347</v>
+        <v>-1498025.1751490347</v>
       </c>
       <c r="Q15" s="29"/>
     </row>
@@ -1896,7 +1896,7 @@
     <row r="17" spans="3:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="56"/>
       <c r="E17" s="76" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F17" s="77"/>
       <c r="G17" s="77"/>
@@ -1904,7 +1904,7 @@
       <c r="I17" s="77"/>
       <c r="J17" s="78"/>
       <c r="K17" s="76" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L17" s="77"/>
       <c r="M17" s="77"/>
@@ -1947,16 +1947,16 @@
         <v>10</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H19" s="28" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I19" s="28" t="s">
         <v>18</v>
@@ -1965,16 +1965,16 @@
         <v>14</v>
       </c>
       <c r="K19" s="28" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L19" s="28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="N19" s="28" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O19" s="28" t="s">
         <v>18</v>
@@ -1990,16 +1990,16 @@
         <v>3</v>
       </c>
       <c r="E20" s="46">
-        <v>0.19624229908494492</v>
+        <v>0.23706203842887777</v>
       </c>
       <c r="F20" s="47">
-        <v>0.11924602038800926</v>
+        <v>0.15568376373572337</v>
       </c>
       <c r="G20" s="46">
-        <v>0.24853825678623254</v>
+        <v>0.26925133042381705</v>
       </c>
       <c r="H20" s="47">
-        <v>0.16512919162771453</v>
+        <v>0.18738159698790705</v>
       </c>
       <c r="I20" s="46">
         <v>0.76085369843675021</v>
@@ -2008,16 +2008,16 @@
         <v>38526.332233379711</v>
       </c>
       <c r="K20" s="46">
-        <v>0.17838120541064889</v>
+        <v>0.21446351214502629</v>
       </c>
       <c r="L20" s="47">
-        <v>0.11456466779026682</v>
+        <v>0.15033403662792774</v>
       </c>
       <c r="M20" s="46">
-        <v>0.22986172036481337</v>
+        <v>0.24849065479845631</v>
       </c>
       <c r="N20" s="47">
-        <v>0.15593569194781073</v>
+        <v>0.17751972279795003</v>
       </c>
       <c r="O20" s="46">
         <v>0.67297911157361623</v>
@@ -2033,40 +2033,40 @@
         <v>7</v>
       </c>
       <c r="E21" s="36">
-        <v>0.51790565571746106</v>
+        <v>0.70708816991849843</v>
       </c>
       <c r="F21" s="37">
-        <v>0.26436020668013616</v>
+        <v>0.38598030176425696</v>
       </c>
       <c r="G21" s="36">
-        <v>0.76673252654976543</v>
+        <v>0.88318103235366763</v>
       </c>
       <c r="H21" s="37">
-        <v>0.48036037555178629</v>
+        <v>0.51823822964717714</v>
       </c>
       <c r="I21" s="36">
-        <v>0.86300694111068021</v>
+        <v>0.85958693843687906</v>
       </c>
       <c r="J21" s="49">
-        <v>-22346.34636354306</v>
+        <v>-20074.34636354306</v>
       </c>
       <c r="K21" s="36">
-        <v>0.46492961224993823</v>
+        <v>0.66374413435416157</v>
       </c>
       <c r="L21" s="37">
-        <v>0.25874389783044904</v>
+        <v>0.36908398409571697</v>
       </c>
       <c r="M21" s="36">
-        <v>0.70264262780933562</v>
+        <v>0.83983699678933066</v>
       </c>
       <c r="N21" s="37">
-        <v>0.47474406670209912</v>
+        <v>0.5013419119786372</v>
       </c>
       <c r="O21" s="36">
-        <v>0.8321906125593006</v>
+        <v>0.83009061091749292</v>
       </c>
       <c r="P21" s="49">
-        <v>-22346.34636354306</v>
+        <v>-20074.34636354306</v>
       </c>
       <c r="Q21" s="29"/>
     </row>
@@ -2076,40 +2076,40 @@
         <v>6</v>
       </c>
       <c r="E22" s="36">
-        <v>0.29557684891275326</v>
+        <v>0.31615295618380845</v>
       </c>
       <c r="F22" s="37">
-        <v>0.17171215149304583</v>
+        <v>0.19693961935362087</v>
       </c>
       <c r="G22" s="36">
-        <v>0.39209706606544248</v>
+        <v>0.45617490877807115</v>
       </c>
       <c r="H22" s="37">
-        <v>0.24037674453728516</v>
+        <v>0.27702681891100189</v>
       </c>
       <c r="I22" s="36">
         <v>0.95078397034395934</v>
       </c>
       <c r="J22" s="49">
-        <v>-55216.198263512342</v>
+        <v>-55206.198263512342</v>
       </c>
       <c r="K22" s="36">
-        <v>0.19616126257082678</v>
+        <v>0.21158740989053368</v>
       </c>
       <c r="L22" s="37">
-        <v>0.14946127532874839</v>
+        <v>0.1746887431893234</v>
       </c>
       <c r="M22" s="36">
-        <v>0.28753151977216768</v>
+        <v>0.35160936248479635</v>
       </c>
       <c r="N22" s="37">
-        <v>0.21812586837298767</v>
+        <v>0.25477594274670445</v>
       </c>
       <c r="O22" s="36">
         <v>0.84721368435551681</v>
       </c>
       <c r="P22" s="49">
-        <v>-55216.198263512342</v>
+        <v>-55206.198263512342</v>
       </c>
       <c r="Q22" s="29"/>
     </row>
@@ -2119,40 +2119,40 @@
         <v>8</v>
       </c>
       <c r="E23" s="36">
-        <v>0.13025655757629329</v>
+        <v>0.35140211698671914</v>
       </c>
       <c r="F23" s="37">
-        <v>7.6077511390222716E-2</v>
+        <v>0.18182364080272367</v>
       </c>
       <c r="G23" s="36">
-        <v>0.48532693965040991</v>
+        <v>0.66722648222217307</v>
       </c>
       <c r="H23" s="37">
-        <v>0.24586305297404137</v>
+        <v>0.33284274463119867</v>
       </c>
       <c r="I23" s="36">
         <v>0.92055337496451972</v>
       </c>
       <c r="J23" s="49">
-        <v>-50776.865686274599</v>
+        <v>-50774.865686274599</v>
       </c>
       <c r="K23" s="36">
-        <v>0.13025655757629329</v>
+        <v>0.35140211698671914</v>
       </c>
       <c r="L23" s="37">
-        <v>7.6077511390222688E-2</v>
+        <v>0.18182364080272362</v>
       </c>
       <c r="M23" s="36">
-        <v>0.46577022517844119</v>
+        <v>0.61701434159061275</v>
       </c>
       <c r="N23" s="37">
-        <v>0.24586305297404132</v>
+        <v>0.33284274463119856</v>
       </c>
       <c r="O23" s="36">
         <v>0.82270899814080067</v>
       </c>
       <c r="P23" s="49">
-        <v>-50776.865686274483</v>
+        <v>-50774.865686274483</v>
       </c>
       <c r="Q23" s="29"/>
     </row>
@@ -2162,16 +2162,16 @@
         <v>28</v>
       </c>
       <c r="E24" s="36">
-        <v>0.25652482193694126</v>
+        <v>0.38106029024545801</v>
       </c>
       <c r="F24" s="37">
-        <v>0.14479107022957827</v>
+        <v>0.23745733638182406</v>
       </c>
       <c r="G24" s="36">
-        <v>0.37276552684930825</v>
+        <v>0.55373602841882852</v>
       </c>
       <c r="H24" s="37">
-        <v>0.23291926976962568</v>
+        <v>0.34566917219641013</v>
       </c>
       <c r="I24" s="36">
         <v>0.95405511089475192</v>
@@ -2180,16 +2180,16 @@
         <v>-805456.20794275973</v>
       </c>
       <c r="K24" s="36">
-        <v>0.15804944790653427</v>
+        <v>0.27151454255876351</v>
       </c>
       <c r="L24" s="37">
-        <v>8.6555079912546018E-2</v>
+        <v>0.16162977246196089</v>
       </c>
       <c r="M24" s="36">
-        <v>0.26321977916261369</v>
+        <v>0.41563961960956181</v>
       </c>
       <c r="N24" s="37">
-        <v>0.15709170584976251</v>
+        <v>0.24570728200538927</v>
       </c>
       <c r="O24" s="36">
         <v>0.78146640969142689</v>
@@ -2205,40 +2205,40 @@
         <v>4</v>
       </c>
       <c r="E25" s="36">
-        <v>0.26598287448626018</v>
+        <v>0.43647539934794072</v>
       </c>
       <c r="F25" s="37">
-        <v>0.12710171949543184</v>
+        <v>0.23339793025084096</v>
       </c>
       <c r="G25" s="36">
-        <v>0.45183513238237083</v>
+        <v>0.56023871307854911</v>
       </c>
       <c r="H25" s="37">
-        <v>0.23492681457071393</v>
+        <v>0.29734334079078217</v>
       </c>
       <c r="I25" s="36">
-        <v>0.90971113398396242</v>
+        <v>0.91030206098743749</v>
       </c>
       <c r="J25" s="49">
-        <v>-18275.308909073239</v>
+        <v>-18934.308909073239</v>
       </c>
       <c r="K25" s="36">
-        <v>0.24084737001038994</v>
+        <v>0.40243421827096798</v>
       </c>
       <c r="L25" s="37">
-        <v>0.12710171949543186</v>
+        <v>0.23339793025084099</v>
       </c>
       <c r="M25" s="36">
-        <v>0.39629237233917319</v>
+        <v>0.46644248929015614</v>
       </c>
       <c r="N25" s="37">
-        <v>0.22506304476508179</v>
+        <v>0.28691046381033891</v>
       </c>
       <c r="O25" s="36">
-        <v>0.80607802018329833</v>
+        <v>0.80748713015553153</v>
       </c>
       <c r="P25" s="49">
-        <v>-18275.308909073297</v>
+        <v>-18934.308909073297</v>
       </c>
       <c r="Q25" s="29"/>
     </row>
@@ -2248,16 +2248,16 @@
         <v>5</v>
       </c>
       <c r="E26" s="36">
-        <v>0.28768341485104493</v>
+        <v>0.43487527023504702</v>
       </c>
       <c r="F26" s="37">
-        <v>0.17691664227870643</v>
+        <v>0.26388472901512827</v>
       </c>
       <c r="G26" s="36">
-        <v>0.37967832446604621</v>
+        <v>0.63983992885726992</v>
       </c>
       <c r="H26" s="37">
-        <v>0.23127169648897006</v>
+        <v>0.38498778979559561</v>
       </c>
       <c r="I26" s="36">
         <v>0.85852148718589438</v>
@@ -2266,16 +2266,16 @@
         <v>-33177.361936059111</v>
       </c>
       <c r="K26" s="36">
-        <v>0.28768341485104493</v>
+        <v>0.43487527023504702</v>
       </c>
       <c r="L26" s="37">
-        <v>0.17691664227870643</v>
+        <v>0.26388472901512827</v>
       </c>
       <c r="M26" s="36">
-        <v>0.37967832446604621</v>
+        <v>0.61845111237178207</v>
       </c>
       <c r="N26" s="37">
-        <v>0.23127169648897006</v>
+        <v>0.38498778979559561</v>
       </c>
       <c r="O26" s="36">
         <v>0.79270724026618655</v>
@@ -2291,40 +2291,40 @@
         <v>9</v>
       </c>
       <c r="E27" s="41">
-        <v>0.29891680868116954</v>
+        <v>0.39598791933304134</v>
       </c>
       <c r="F27" s="42">
-        <v>0.15463729808695156</v>
+        <v>0.20557113844907493</v>
       </c>
       <c r="G27" s="41">
-        <v>0.49258105352885184</v>
+        <v>0.59295181288414001</v>
       </c>
       <c r="H27" s="42">
-        <v>0.25828113019585963</v>
+        <v>0.31135877216931823</v>
       </c>
       <c r="I27" s="41">
-        <v>0.91359695125093066</v>
+        <v>0.91381578676474506</v>
       </c>
       <c r="J27" s="43">
-        <v>-554962.21828119573</v>
+        <v>-552928.21828119573</v>
       </c>
       <c r="K27" s="41">
-        <v>0.26924360064712644</v>
+        <v>0.34872195540275586</v>
       </c>
       <c r="L27" s="42">
-        <v>0.14436306670456331</v>
+        <v>0.19506267050664539</v>
       </c>
       <c r="M27" s="41">
-        <v>0.4209318457130668</v>
+        <v>0.50854117074371641</v>
       </c>
       <c r="N27" s="42">
-        <v>0.23939568236754402</v>
+        <v>0.28760659091203433</v>
       </c>
       <c r="O27" s="41">
-        <v>0.81386093126731651</v>
+        <v>0.81371058113332673</v>
       </c>
       <c r="P27" s="43">
-        <v>-554962.21828119573</v>
+        <v>-552928.21828119573</v>
       </c>
       <c r="Q27" s="29"/>
     </row>
@@ -2334,40 +2334,40 @@
         <v>2</v>
       </c>
       <c r="E28" s="44">
-        <v>0.25740583167526399</v>
+        <v>0.35940647641655027</v>
       </c>
       <c r="F28" s="44">
-        <v>0.14073469357812013</v>
+        <v>0.20397081279794724</v>
       </c>
       <c r="G28" s="44">
-        <v>0.41258354695416499</v>
+        <v>0.51939431320021368</v>
       </c>
       <c r="H28" s="44">
-        <v>0.23410330676755803</v>
+        <v>0.29600120121001711</v>
       </c>
       <c r="I28" s="44">
-        <v>0.89103917736327809</v>
+        <v>0.89117307970904136</v>
       </c>
       <c r="J28" s="45">
-        <v>-1501684.1751490394</v>
+        <v>-1498025.1751490394</v>
       </c>
       <c r="K28" s="44">
-        <v>0.22125003200791082</v>
+        <v>0.31303127087740951</v>
       </c>
       <c r="L28" s="44">
-        <v>0.1275769076232614</v>
+        <v>0.1885641143800206</v>
       </c>
       <c r="M28" s="44">
-        <v>0.3541346841589707</v>
+        <v>0.44557913043010267</v>
       </c>
       <c r="N28" s="44">
-        <v>0.21365279662169914</v>
+        <v>0.27058226538417318</v>
       </c>
       <c r="O28" s="44">
-        <v>0.78659075457362893</v>
+        <v>0.78665301433907575</v>
       </c>
       <c r="P28" s="45">
-        <v>-1501684.1751490347</v>
+        <v>-1498025.1751490347</v>
       </c>
       <c r="Q28" s="50"/>
     </row>
@@ -2505,13 +2505,13 @@
         <v>22</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>20</v>
@@ -2520,17 +2520,17 @@
         <v>19</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="8" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q4" s="10"/>
       <c r="R4" s="8" t="s">
@@ -2546,7 +2546,7 @@
         <v>24</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="W4" s="11"/>
     </row>
@@ -2559,16 +2559,16 @@
         <v>3</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="15">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="G5" s="22">
-        <v>4158</v>
+        <v>14067</v>
       </c>
       <c r="H5" s="22">
-        <v>11177.068672557696</v>
+        <v>41079.565437224679</v>
       </c>
       <c r="I5" s="23">
         <v>0</v>
@@ -2594,13 +2594,13 @@
       </c>
       <c r="Q5" s="10"/>
       <c r="R5" s="17">
-        <v>1</v>
+        <v>0.37488225194429953</v>
       </c>
       <c r="S5" s="23">
-        <v>-5142.9313274423039</v>
+        <v>25679.565437224679</v>
       </c>
       <c r="T5" s="24">
-        <v>16320</v>
+        <v>15400</v>
       </c>
       <c r="U5" s="24">
         <v>0</v>
@@ -2617,16 +2617,16 @@
         <v>3</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="15">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G6" s="22">
-        <v>14067</v>
+        <v>155051</v>
       </c>
       <c r="H6" s="22">
-        <v>41079.565437224679</v>
+        <v>218978.14593548569</v>
       </c>
       <c r="I6" s="23">
         <v>0</v>
@@ -2652,13 +2652,13 @@
       </c>
       <c r="Q6" s="10"/>
       <c r="R6" s="17">
-        <v>0.37488225194429953</v>
+        <v>1</v>
       </c>
       <c r="S6" s="23">
-        <v>25679.565437224679</v>
+        <v>-74685.854064514308</v>
       </c>
       <c r="T6" s="24">
-        <v>15400</v>
+        <v>293664</v>
       </c>
       <c r="U6" s="24">
         <v>0</v>
@@ -2669,54 +2669,54 @@
     <row r="7" spans="2:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6"/>
       <c r="C7" s="12" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F7" s="15">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G7" s="22">
-        <v>155051</v>
+        <v>52771</v>
       </c>
       <c r="H7" s="22">
-        <v>218978.14593548569</v>
+        <v>71853.815174981937</v>
       </c>
       <c r="I7" s="23">
-        <v>0</v>
+        <v>6720</v>
       </c>
       <c r="J7" s="23">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="K7" s="23">
-        <v>0</v>
+        <v>15120</v>
       </c>
       <c r="L7" s="16">
-        <v>0</v>
+        <v>0.12734266926910615</v>
       </c>
       <c r="M7" s="16">
-        <v>0</v>
+        <v>9.3523217711336912E-2</v>
       </c>
       <c r="N7" s="10"/>
       <c r="O7" s="17">
-        <v>0</v>
+        <v>0.28652100585548879</v>
       </c>
       <c r="P7" s="17">
-        <v>0</v>
+        <v>0.21042723985050807</v>
       </c>
       <c r="Q7" s="10"/>
       <c r="R7" s="17">
-        <v>1</v>
+        <v>0.93523217711336915</v>
       </c>
       <c r="S7" s="23">
-        <v>-74685.854064514308</v>
+        <v>4653.8151749819372</v>
       </c>
       <c r="T7" s="24">
-        <v>293664</v>
+        <v>60480</v>
       </c>
       <c r="U7" s="24">
         <v>0</v>
@@ -2733,48 +2733,48 @@
         <v>6</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F8" s="15">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G8" s="22">
-        <v>52771</v>
+        <v>21255</v>
       </c>
       <c r="H8" s="22">
-        <v>71853.815174981937</v>
+        <v>28660.652586976066</v>
       </c>
       <c r="I8" s="23">
-        <v>6720</v>
+        <v>2000</v>
       </c>
       <c r="J8" s="23">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="K8" s="23">
-        <v>6720</v>
+        <v>6800</v>
       </c>
       <c r="L8" s="16">
-        <v>0.12734266926910615</v>
+        <v>9.4095506939543633E-2</v>
       </c>
       <c r="M8" s="16">
-        <v>9.3523217711336912E-2</v>
+        <v>6.9782081686054737E-2</v>
       </c>
       <c r="N8" s="10"/>
       <c r="O8" s="17">
-        <v>0.12734266926910615</v>
+        <v>0.31992472359444835</v>
       </c>
       <c r="P8" s="17">
-        <v>9.3523217711336912E-2</v>
+        <v>0.23725907773258612</v>
       </c>
       <c r="Q8" s="10"/>
       <c r="R8" s="17">
-        <v>0.93523217711336915</v>
+        <v>1</v>
       </c>
       <c r="S8" s="23">
-        <v>4653.8151749819372</v>
+        <v>-3339.3474130239338</v>
       </c>
       <c r="T8" s="24">
-        <v>60480</v>
+        <v>30000</v>
       </c>
       <c r="U8" s="24">
         <v>0</v>
@@ -2791,7 +2791,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="15">
         <v>13</v>
@@ -2846,28 +2846,28 @@
         <v>11</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F10" s="15">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G10" s="22">
-        <v>29369</v>
+        <v>12759</v>
       </c>
       <c r="H10" s="22">
-        <v>43593.182800043389</v>
+        <v>26915.301227842272</v>
       </c>
       <c r="I10" s="23">
         <v>0</v>
       </c>
       <c r="J10" s="23">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="K10" s="23">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="L10" s="16">
         <v>0</v>
@@ -2877,20 +2877,20 @@
       </c>
       <c r="N10" s="10"/>
       <c r="O10" s="17">
-        <v>0</v>
+        <v>0.37620503174229958</v>
       </c>
       <c r="P10" s="17">
-        <v>0</v>
+        <v>0.17833722013241624</v>
       </c>
       <c r="Q10" s="10"/>
       <c r="R10" s="17">
         <v>1</v>
       </c>
       <c r="S10" s="23">
-        <v>-9206.8171999566111</v>
+        <v>-10260.698772157728</v>
       </c>
       <c r="T10" s="24">
-        <v>52800</v>
+        <v>37176</v>
       </c>
       <c r="U10" s="24">
         <v>0</v>
@@ -2907,25 +2907,25 @@
         <v>28</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F11" s="15">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G11" s="22">
-        <v>14343</v>
+        <v>29369</v>
       </c>
       <c r="H11" s="22">
-        <v>33069.517587662376</v>
+        <v>43593.182800043389</v>
       </c>
       <c r="I11" s="23">
         <v>0</v>
       </c>
       <c r="J11" s="23">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="K11" s="23">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="L11" s="16">
         <v>0</v>
@@ -2935,20 +2935,20 @@
       </c>
       <c r="N11" s="10"/>
       <c r="O11" s="17">
-        <v>0</v>
+        <v>0.32687527665225236</v>
       </c>
       <c r="P11" s="17">
-        <v>0</v>
+        <v>0.22021791902724858</v>
       </c>
       <c r="Q11" s="10"/>
       <c r="R11" s="17">
         <v>1</v>
       </c>
       <c r="S11" s="23">
-        <v>-2882.4824123376238</v>
+        <v>-9206.8171999566111</v>
       </c>
       <c r="T11" s="24">
-        <v>35952</v>
+        <v>52800</v>
       </c>
       <c r="U11" s="24">
         <v>0</v>
@@ -2965,25 +2965,25 @@
         <v>28</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F12" s="15">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G12" s="22">
-        <v>19895</v>
+        <v>14343</v>
       </c>
       <c r="H12" s="22">
-        <v>32777.41672791609</v>
+        <v>33069.517587662376</v>
       </c>
       <c r="I12" s="23">
         <v>0</v>
       </c>
       <c r="J12" s="23">
-        <v>0</v>
+        <v>4320</v>
       </c>
       <c r="K12" s="23">
-        <v>0</v>
+        <v>4320</v>
       </c>
       <c r="L12" s="16">
         <v>0</v>
@@ -2993,20 +2993,20 @@
       </c>
       <c r="N12" s="10"/>
       <c r="O12" s="17">
-        <v>0</v>
+        <v>0.30119221920100397</v>
       </c>
       <c r="P12" s="17">
-        <v>0</v>
+        <v>0.13063389837932537</v>
       </c>
       <c r="Q12" s="10"/>
       <c r="R12" s="17">
         <v>1</v>
       </c>
       <c r="S12" s="23">
-        <v>-19302.58327208391</v>
+        <v>-2882.4824123376238</v>
       </c>
       <c r="T12" s="24">
-        <v>52080</v>
+        <v>35952</v>
       </c>
       <c r="U12" s="24">
         <v>0</v>
@@ -3020,51 +3020,51 @@
         <v>11</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F13" s="15">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G13" s="22">
-        <v>48355</v>
+        <v>19895</v>
       </c>
       <c r="H13" s="22">
-        <v>93846.640060946898</v>
+        <v>32777.41672791609</v>
       </c>
       <c r="I13" s="23">
-        <v>6492</v>
+        <v>0</v>
       </c>
       <c r="J13" s="23">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="K13" s="23">
-        <v>10692</v>
+        <v>0</v>
       </c>
       <c r="L13" s="16">
-        <v>0.13425705718126357</v>
+        <v>0</v>
       </c>
       <c r="M13" s="16">
-        <v>6.9176690777463051E-2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="10"/>
       <c r="O13" s="17">
-        <v>0.22111467273291283</v>
+        <v>0</v>
       </c>
       <c r="P13" s="17">
-        <v>0.11393055726935228</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="17">
-        <v>0.9872702948110762</v>
+        <v>1</v>
       </c>
       <c r="S13" s="23">
-        <v>1194.6400609468983</v>
+        <v>-19302.58327208391</v>
       </c>
       <c r="T13" s="24">
-        <v>86160</v>
+        <v>52080</v>
       </c>
       <c r="U13" s="24">
         <v>0</v>
@@ -3078,51 +3078,51 @@
         <v>11</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E14" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="15">
         <v>38</v>
       </c>
-      <c r="F14" s="15">
-        <v>17</v>
-      </c>
       <c r="G14" s="22">
-        <v>35527</v>
+        <v>13884</v>
       </c>
       <c r="H14" s="22">
-        <v>68222.494575322227</v>
+        <v>26180.673299976392</v>
       </c>
       <c r="I14" s="23">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J14" s="23">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="K14" s="23">
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="L14" s="16">
-        <v>0</v>
+        <v>0.34572169403630076</v>
       </c>
       <c r="M14" s="16">
-        <v>0</v>
+        <v>0.1833413505069913</v>
       </c>
       <c r="N14" s="10"/>
       <c r="O14" s="17">
-        <v>0.1013313817659808</v>
+        <v>0.34572169403630076</v>
       </c>
       <c r="P14" s="17">
-        <v>5.2768518982039825E-2</v>
+        <v>0.1833413505069913</v>
       </c>
       <c r="Q14" s="10"/>
       <c r="R14" s="17">
-        <v>1</v>
+        <v>0.97170915768705379</v>
       </c>
       <c r="S14" s="23">
-        <v>-10177.505424677773</v>
+        <v>740.67329997639172</v>
       </c>
       <c r="T14" s="24">
-        <v>78400</v>
+        <v>20640</v>
       </c>
       <c r="U14" s="24">
         <v>0</v>
@@ -3133,54 +3133,54 @@
     <row r="15" spans="2:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="6"/>
       <c r="C15" s="12" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F15" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G15" s="22">
-        <v>56737</v>
+        <v>48355</v>
       </c>
       <c r="H15" s="22">
-        <v>112369.6457218524</v>
+        <v>93846.640060946898</v>
       </c>
       <c r="I15" s="23">
-        <v>9563</v>
+        <v>10692</v>
       </c>
       <c r="J15" s="23">
-        <v>4608</v>
+        <v>6000</v>
       </c>
       <c r="K15" s="23">
-        <v>14171</v>
+        <v>16692</v>
       </c>
       <c r="L15" s="16">
-        <v>0.16854962370234591</v>
+        <v>0.22111467273291283</v>
       </c>
       <c r="M15" s="16">
-        <v>8.5103053752355953E-2</v>
+        <v>0.11393055726935228</v>
       </c>
       <c r="N15" s="10"/>
       <c r="O15" s="17">
-        <v>0.24976646632708815</v>
+        <v>0.34519698066384036</v>
       </c>
       <c r="P15" s="17">
-        <v>0.12611056935319839</v>
+        <v>0.17786465225776546</v>
       </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="17">
-        <v>0.90525336576920468</v>
+        <v>0.9872702948110762</v>
       </c>
       <c r="S15" s="23">
-        <v>10646.645721852401</v>
+        <v>1194.6400609468983</v>
       </c>
       <c r="T15" s="24">
-        <v>92160</v>
+        <v>81960</v>
       </c>
       <c r="U15" s="24">
         <v>0</v>
@@ -3197,48 +3197,48 @@
         <v>9</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F16" s="15">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G16" s="22">
-        <v>17279</v>
+        <v>56737</v>
       </c>
       <c r="H16" s="22">
-        <v>39244.41031976504</v>
+        <v>112369.6457218524</v>
       </c>
       <c r="I16" s="23">
-        <v>0</v>
+        <v>13243</v>
       </c>
       <c r="J16" s="23">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="K16" s="23">
-        <v>2400</v>
+        <v>13243</v>
       </c>
       <c r="L16" s="16">
-        <v>0</v>
+        <v>0.23341029663182755</v>
       </c>
       <c r="M16" s="16">
-        <v>0</v>
+        <v>0.11785211135025095</v>
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="17">
-        <v>0.13889692690549221</v>
+        <v>0.23341029663182755</v>
       </c>
       <c r="P16" s="17">
-        <v>6.1155206064881673E-2</v>
+        <v>0.11785211135025095</v>
       </c>
       <c r="Q16" s="10"/>
       <c r="R16" s="17">
-        <v>1</v>
+        <v>0.90148010478509943</v>
       </c>
       <c r="S16" s="23">
-        <v>-38755.58968023496</v>
+        <v>11070.645721852401</v>
       </c>
       <c r="T16" s="24">
-        <v>78000</v>
+        <v>88056</v>
       </c>
       <c r="U16" s="24">
         <v>0</v>
@@ -3258,45 +3258,45 @@
         <v>54</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G17" s="22">
-        <v>34107</v>
+        <v>17432</v>
       </c>
       <c r="H17" s="22">
-        <v>65099.519357498437</v>
+        <v>35295.66572007291</v>
       </c>
       <c r="I17" s="23">
-        <v>4584</v>
+        <v>7188</v>
       </c>
       <c r="J17" s="23">
         <v>0</v>
       </c>
       <c r="K17" s="23">
-        <v>4584</v>
+        <v>7188</v>
       </c>
       <c r="L17" s="16">
-        <v>0.134400562934295</v>
+        <v>0.41234511243689764</v>
       </c>
       <c r="M17" s="16">
-        <v>7.04152664296437E-2</v>
+        <v>0.20365106744288239</v>
       </c>
       <c r="N17" s="10"/>
       <c r="O17" s="17">
-        <v>0.134400562934295</v>
+        <v>0.41234511243689764</v>
       </c>
       <c r="P17" s="17">
-        <v>7.04152664296437E-2</v>
+        <v>0.20365106744288239</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="17">
-        <v>1</v>
+        <v>0.81188438907112381</v>
       </c>
       <c r="S17" s="23">
-        <v>-9036.4806425015631</v>
+        <v>6639.6657200729096</v>
       </c>
       <c r="T17" s="24">
-        <v>69552</v>
+        <v>21468</v>
       </c>
       <c r="U17" s="24">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>9</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F18" s="15">
         <v>24</v>
@@ -3325,26 +3325,26 @@
         <v>18264.470861812257</v>
       </c>
       <c r="I18" s="23">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="J18" s="23">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K18" s="23">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="L18" s="16">
-        <v>0</v>
+        <v>0.16169238024658089</v>
       </c>
       <c r="M18" s="16">
-        <v>0</v>
+        <v>0.13140265700321879</v>
       </c>
       <c r="N18" s="10"/>
       <c r="O18" s="17">
-        <v>0</v>
+        <v>0.24253857036987131</v>
       </c>
       <c r="P18" s="17">
-        <v>0</v>
+        <v>0.19710398550482819</v>
       </c>
       <c r="Q18" s="10"/>
       <c r="R18" s="17">
@@ -3354,7 +3354,7 @@
         <v>4152.4708618122568</v>
       </c>
       <c r="T18" s="24">
-        <v>14112</v>
+        <v>11712</v>
       </c>
       <c r="U18" s="24">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="15">
         <v>12</v>
